--- a/outputs/Block2_2026_Target_Stability_v12.xlsx
+++ b/outputs/Block2_2026_Target_Stability_v12.xlsx
@@ -70,25 +70,34 @@
     <t>Fold Mean Role</t>
   </si>
   <si>
+    <t>RHouSafResH (&gt;10%)</t>
+  </si>
+  <si>
+    <t>D House After</t>
+  </si>
+  <si>
+    <t>R House After</t>
+  </si>
+  <si>
     <t>DHouSafResH (&gt;5%&lt;=10%)</t>
   </si>
   <si>
-    <t>D House After</t>
+    <t>R House Seats Lost</t>
   </si>
   <si>
     <t>D House Seats LOST</t>
   </si>
   <si>
-    <t>R House After</t>
-  </si>
-  <si>
-    <t>RHouSafResH (&gt;10%)</t>
+    <t>D Senate After</t>
   </si>
   <si>
     <t>DHouLikResH (&gt;5%&lt;=10%)</t>
   </si>
   <si>
-    <t>R House Seats Lost</t>
+    <t>DHouSafResLR (&gt;10%)</t>
+  </si>
+  <si>
+    <t>R Senate After</t>
   </si>
   <si>
     <t>RHouLeanResLD  (&gt;1&lt;=5%)</t>
@@ -100,100 +109,91 @@
     <t>D Senate Seats LOST</t>
   </si>
   <si>
+    <t>DHouLeanResH  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>RHouLikResLD (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>DHouLeanResLR  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
     <t>DHouLikResLR (&gt;5%&lt;=10%)</t>
   </si>
   <si>
-    <t>DHouSafResLR (&gt;10%)</t>
-  </si>
-  <si>
-    <t>D Senate After</t>
-  </si>
-  <si>
-    <t>DHouLeanResH  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>DHouLeanResLR  (&gt;1&lt;=5%)</t>
+    <t>DSenSafResH (&gt;10%)</t>
   </si>
   <si>
     <t>DSenSafResLR (&gt;10%)</t>
   </si>
   <si>
-    <t>R Senate After</t>
-  </si>
-  <si>
     <t>R Senate Seats LOST</t>
   </si>
   <si>
     <t>RHouLeanResH  (&gt;1&lt;=5%)</t>
   </si>
   <si>
-    <t>RHouLikResLD (&gt;5%&lt;=10%)</t>
+    <t>RHouSafResLD (&gt;10%)</t>
+  </si>
+  <si>
+    <t>DHouTiltResH (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>DHouTiltResLR (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>DSenLeanResLR  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>DSenLikResH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>DSenLikResLR (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>DSenTiltResH (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>RHouTiltResH (&lt;=1%)</t>
   </si>
   <si>
     <t>RHouTiltResLD (&lt;=1%)</t>
   </si>
   <si>
-    <t>DHouTiltResH (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>DHouTiltResLR (&lt;=1%)</t>
+    <t>RSenLeanResH  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>RSenLikResH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>RSenLikResLD (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>RSenSafResH (&gt;10%)</t>
+  </si>
+  <si>
+    <t>RSenSafResLD (&gt;10%)</t>
+  </si>
+  <si>
+    <t>RSenTiltResH (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>RSenTiltResLD (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>DPP</t>
+  </si>
+  <si>
+    <t>RPP</t>
   </si>
   <si>
     <t>DSenLeanResH  (&gt;1&lt;=5%)</t>
   </si>
   <si>
-    <t>DSenLeanResLR  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>DSenLikResLR (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>DSenSafResH (&gt;10%)</t>
-  </si>
-  <si>
-    <t>DSenTiltResH (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>RHouSafResLD (&gt;10%)</t>
-  </si>
-  <si>
-    <t>RHouTiltResH (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>RSenLeanResH  (&gt;1&lt;=5%)</t>
+    <t>DSenTiltResLR (&lt;=1%)</t>
   </si>
   <si>
     <t>RSenLeanResLD  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>RSenLikResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RSenLikResLD (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RSenSafResH (&gt;10%)</t>
-  </si>
-  <si>
-    <t>RSenSafResLD (&gt;10%)</t>
-  </si>
-  <si>
-    <t>RSenTiltResH (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>RSenTiltResLD (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>DPP</t>
-  </si>
-  <si>
-    <t>RPP</t>
-  </si>
-  <si>
-    <t>DSenLikResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>DSenTiltResLR (&lt;=1%)</t>
   </si>
   <si>
     <t>House Buckets</t>
@@ -654,37 +654,37 @@
         <v>66</v>
       </c>
       <c r="E2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F2">
-        <v>179.4</v>
+        <v>174.8</v>
       </c>
       <c r="G2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H2">
-        <v>-1.599999999999994</v>
+        <v>0.8000000000000114</v>
       </c>
       <c r="I2">
-        <v>7.893034904268447</v>
+        <v>9.338094023943002</v>
       </c>
       <c r="J2">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="K2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="L2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N2">
-        <v>18.8</v>
+        <v>12.2</v>
       </c>
       <c r="O2">
-        <v>0.5319148936170213</v>
+        <v>1.229508196721312</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -710,37 +710,37 @@
         <v>66</v>
       </c>
       <c r="E3">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F3">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="G3">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="H3">
         <v>-1</v>
       </c>
       <c r="I3">
-        <v>6.284902544988268</v>
+        <v>9.273618495495704</v>
       </c>
       <c r="J3">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="K3">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L3">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="M3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N3">
         <v>18.6</v>
       </c>
       <c r="O3">
-        <v>0.4301075268817204</v>
+        <v>0.7526881720430108</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
@@ -766,37 +766,37 @@
         <v>66</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>216</v>
       </c>
       <c r="F4">
-        <v>8.6</v>
+        <v>217</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="H4">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>4.827007354458869</v>
+        <v>9.273618495495704</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>202</v>
       </c>
       <c r="K4">
+        <v>226</v>
+      </c>
+      <c r="L4">
+        <v>24</v>
+      </c>
+      <c r="M4">
         <v>14</v>
       </c>
-      <c r="L4">
-        <v>11</v>
-      </c>
-      <c r="M4">
-        <v>8</v>
-      </c>
       <c r="N4">
-        <v>16</v>
+        <v>18.6</v>
       </c>
       <c r="O4">
-        <v>0.5</v>
+        <v>0.7526881720430108</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
@@ -813,46 +813,46 @@
         <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
         <v>66</v>
       </c>
       <c r="E5">
-        <v>212</v>
+        <v>174</v>
       </c>
       <c r="F5">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="G5">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="I5">
-        <v>6.284902544988268</v>
+        <v>7.176350047203662</v>
       </c>
       <c r="J5">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="K5">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="L5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N5">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="O5">
-        <v>0.4301075268817204</v>
+        <v>0.5319148936170213</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
@@ -869,46 +869,46 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
         <v>66</v>
       </c>
       <c r="E6">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>172.4</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>173</v>
+        <v>14</v>
       </c>
       <c r="H6">
-        <v>1.400000000000006</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>3.974921382870358</v>
+        <v>6.442049363362563</v>
       </c>
       <c r="J6">
-        <v>167</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="L6">
+        <v>16</v>
+      </c>
+      <c r="M6">
         <v>10</v>
       </c>
-      <c r="M6">
-        <v>6</v>
-      </c>
       <c r="N6">
-        <v>12.2</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>0.4918032786885246</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
@@ -925,46 +925,46 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
         <v>66</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>17.8</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H7">
-        <v>-1.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>2.280350850198276</v>
+        <v>4.358898943540674</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L7">
+        <v>10</v>
+      </c>
+      <c r="M7">
         <v>6</v>
       </c>
-      <c r="M7">
-        <v>5</v>
-      </c>
       <c r="N7">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="O7">
-        <v>0.9615384615384615</v>
+        <v>0.375</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
@@ -990,37 +990,37 @@
         <v>66</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="F8">
-        <v>15.6</v>
+        <v>48.6</v>
       </c>
       <c r="G8">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="H8">
-        <v>1.6</v>
+        <v>-1.399999999999999</v>
       </c>
       <c r="I8">
-        <v>2.408318915758459</v>
+        <v>1.816590212458495</v>
       </c>
       <c r="J8">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="K8">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="L8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="O8">
-        <v>0.5555555555555556</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
@@ -1046,37 +1046,37 @@
         <v>66</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F9">
-        <v>4.8</v>
+        <v>17.4</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H9">
-        <v>0.7999999999999998</v>
+        <v>-1.600000000000001</v>
       </c>
       <c r="I9">
-        <v>1.788854381999832</v>
+        <v>1.949358868961793</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K9">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>4</v>
       </c>
       <c r="N9">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="O9">
-        <v>1.111111111111111</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
@@ -1102,25 +1102,25 @@
         <v>66</v>
       </c>
       <c r="E10">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>15.6</v>
+        <v>2.6</v>
       </c>
       <c r="G10">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H10">
-        <v>-1.4</v>
+        <v>1.6</v>
       </c>
       <c r="I10">
-        <v>2.302172886644267</v>
+        <v>2.509980079602227</v>
       </c>
       <c r="J10">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -1129,10 +1129,10 @@
         <v>4</v>
       </c>
       <c r="N10">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="O10">
-        <v>0.7407407407407407</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
@@ -1158,37 +1158,37 @@
         <v>66</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F11">
-        <v>1.4</v>
+        <v>51.4</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="H11">
-        <v>0.3999999999999999</v>
+        <v>1.399999999999999</v>
       </c>
       <c r="I11">
-        <v>1.673320053068151</v>
+        <v>1.816590212458495</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="K11">
+        <v>54</v>
+      </c>
+      <c r="L11">
+        <v>5</v>
+      </c>
+      <c r="M11">
         <v>4</v>
       </c>
-      <c r="L11">
-        <v>4</v>
-      </c>
-      <c r="M11">
-        <v>3</v>
-      </c>
       <c r="N11">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="O11">
-        <v>1.25</v>
+        <v>1.538461538461538</v>
       </c>
       <c r="P11" t="b">
         <v>1</v>
@@ -1214,37 +1214,37 @@
         <v>66</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0.5999999999999996</v>
       </c>
       <c r="I12">
-        <v>1.414213562373095</v>
+        <v>2.880972058177587</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N12">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="O12">
-        <v>0.5</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="P12" t="b">
         <v>1</v>
@@ -1270,37 +1270,37 @@
         <v>66</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F13">
-        <v>1.2</v>
+        <v>14.6</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H13">
-        <v>1.2</v>
+        <v>-0.4000000000000004</v>
       </c>
       <c r="I13">
-        <v>1.643167672515498</v>
+        <v>2.880972058177587</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K13">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N13">
-        <v>8.6</v>
+        <v>5.4</v>
       </c>
       <c r="O13">
-        <v>0.3488372093023256</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="P13" t="b">
         <v>1</v>
@@ -1326,37 +1326,37 @@
         <v>66</v>
       </c>
       <c r="E14">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>48.4</v>
+        <v>1.4</v>
       </c>
       <c r="G14">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>0.3999999999999986</v>
+        <v>1.4</v>
       </c>
       <c r="I14">
-        <v>1.51657508881031</v>
+        <v>1.140175425099138</v>
       </c>
       <c r="J14">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="L14">
         <v>3</v>
       </c>
       <c r="M14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N14">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="O14">
-        <v>0.7142857142857143</v>
+        <v>1.25</v>
       </c>
       <c r="P14" t="b">
         <v>1</v>
@@ -1382,37 +1382,37 @@
         <v>66</v>
       </c>
       <c r="E15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F15">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="G15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H15">
-        <v>0.5999999999999996</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="I15">
-        <v>1.673320053068151</v>
+        <v>1.949358868961793</v>
       </c>
       <c r="J15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N15">
         <v>3.2</v>
       </c>
       <c r="O15">
-        <v>0.625</v>
+        <v>0.9375</v>
       </c>
       <c r="P15" t="b">
         <v>1</v>
@@ -1441,34 +1441,34 @@
         <v>5</v>
       </c>
       <c r="F16">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H16">
-        <v>0.2000000000000002</v>
+        <v>-0.4000000000000004</v>
       </c>
       <c r="I16">
-        <v>1.30384048104053</v>
+        <v>2.073644135332772</v>
       </c>
       <c r="J16">
         <v>3</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L16">
+        <v>5</v>
+      </c>
+      <c r="M16">
         <v>3</v>
       </c>
-      <c r="M16">
-        <v>2</v>
-      </c>
       <c r="N16">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="O16">
-        <v>0.7692307692307692</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="P16" t="b">
         <v>1</v>
@@ -1485,7 +1485,7 @@
         <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
         <v>64</v>
@@ -1494,37 +1494,37 @@
         <v>66</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F17">
-        <v>0.6</v>
+        <v>5.6</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H17">
-        <v>0.6</v>
+        <v>-0.4000000000000004</v>
       </c>
       <c r="I17">
-        <v>0.8944271909999159</v>
+        <v>1.51657508881031</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K17">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M17">
         <v>2</v>
       </c>
       <c r="N17">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="O17">
-        <v>1.666666666666667</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="P17" t="b">
         <v>1</v>
@@ -1541,46 +1541,46 @@
         <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
         <v>66</v>
       </c>
       <c r="E18">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>51.6</v>
+        <v>2.2</v>
       </c>
       <c r="G18">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="H18">
-        <v>-0.3999999999999986</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="I18">
-        <v>1.51657508881031</v>
+        <v>1.643167672515498</v>
       </c>
       <c r="J18">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="L18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M18">
         <v>2</v>
       </c>
       <c r="N18">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>0.7692307692307692</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="P18" t="b">
         <v>1</v>
@@ -1597,34 +1597,34 @@
         <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
         <v>66</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F19">
-        <v>2.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H19">
-        <v>0.7999999999999998</v>
+        <v>-1.199999999999999</v>
       </c>
       <c r="I19">
         <v>0.8366600265340756</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>2</v>
@@ -1633,10 +1633,10 @@
         <v>2</v>
       </c>
       <c r="N19">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="O19">
-        <v>1.428571428571429</v>
+        <v>1</v>
       </c>
       <c r="P19" t="b">
         <v>1</v>
@@ -1653,7 +1653,7 @@
         <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s">
         <v>64</v>
@@ -1662,37 +1662,37 @@
         <v>66</v>
       </c>
       <c r="E20">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>13</v>
+        <v>0.8</v>
       </c>
       <c r="G20">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>0.8</v>
       </c>
       <c r="I20">
-        <v>1.414213562373095</v>
+        <v>0.8366600265340756</v>
       </c>
       <c r="J20">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M20">
         <v>2</v>
       </c>
       <c r="N20">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="O20">
-        <v>0.9090909090909091</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="P20" t="b">
         <v>1</v>
@@ -1709,46 +1709,46 @@
         <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D21" t="s">
         <v>66</v>
       </c>
       <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21">
+        <v>3</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>1.224744871391589</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
         <v>4</v>
       </c>
-      <c r="F21">
-        <v>4.8</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-      <c r="H21">
-        <v>0.7999999999999998</v>
-      </c>
-      <c r="I21">
-        <v>0.8366600265340756</v>
-      </c>
-      <c r="J21">
-        <v>4</v>
-      </c>
-      <c r="K21">
-        <v>6</v>
-      </c>
       <c r="L21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21">
         <v>2</v>
       </c>
       <c r="N21">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="O21">
-        <v>0.5555555555555556</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="P21" t="b">
         <v>1</v>
@@ -1774,25 +1774,25 @@
         <v>66</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F22">
-        <v>2.4</v>
+        <v>12.4</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H22">
-        <v>-0.6000000000000001</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="I22">
         <v>1.140175425099138</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K22">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L22">
         <v>3</v>
@@ -1801,10 +1801,10 @@
         <v>2</v>
       </c>
       <c r="N22">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="O22">
-        <v>1.666666666666667</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="P22" t="b">
         <v>1</v>
@@ -1830,37 +1830,37 @@
         <v>66</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F23">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H23">
-        <v>-0.4</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="I23">
-        <v>0.5477225575051662</v>
+        <v>1.483239697419133</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N23">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="O23">
-        <v>1.25</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="P23" t="b">
         <v>1</v>
@@ -1892,31 +1892,31 @@
         <v>1.2</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>0.2</v>
       </c>
       <c r="I24">
-        <v>1.095445115010332</v>
+        <v>0.4472135954999579</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24">
         <v>2</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M24">
         <v>1</v>
       </c>
       <c r="N24">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="O24">
-        <v>0.625</v>
+        <v>1.25</v>
       </c>
       <c r="P24" t="b">
         <v>1</v>
@@ -1933,7 +1933,7 @@
         <v>41</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
         <v>64</v>
@@ -1942,25 +1942,25 @@
         <v>66</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25">
-        <v>-0.2</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="I25">
-        <v>0.4472135954999579</v>
+        <v>0.5477225575051661</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25">
         <v>1</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="N25">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="O25">
-        <v>1.25</v>
+        <v>0.625</v>
       </c>
       <c r="P25" t="b">
         <v>1</v>
@@ -1998,7 +1998,7 @@
         <v>66</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>0.4</v>
@@ -2007,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>-0.6</v>
+        <v>0.4</v>
       </c>
       <c r="I26">
         <v>0.5477225575051662</v>
@@ -2054,25 +2054,25 @@
         <v>66</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I27">
-        <v>0.5477225575051662</v>
+        <v>0.4472135954999579</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27">
         <v>1</v>
@@ -2081,10 +2081,10 @@
         <v>1</v>
       </c>
       <c r="N27">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O27">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="P27" t="b">
         <v>1</v>
@@ -2110,37 +2110,37 @@
         <v>66</v>
       </c>
       <c r="E28">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>9</v>
+        <v>0.2</v>
       </c>
       <c r="G28">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>0.447213595499958</v>
       </c>
       <c r="J28">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28">
         <v>1</v>
       </c>
       <c r="N28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O28">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P28" t="b">
         <v>1</v>
@@ -2169,16 +2169,16 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="I29">
-        <v>0.4472135954999579</v>
+        <v>0.5477225575051662</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -2225,34 +2225,34 @@
         <v>3</v>
       </c>
       <c r="F30">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="G30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H30">
-        <v>0.6000000000000001</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="I30">
-        <v>0.8944271909999161</v>
+        <v>0.4472135954999579</v>
       </c>
       <c r="J30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30">
         <v>4</v>
       </c>
       <c r="L30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M30">
         <v>1</v>
       </c>
       <c r="N30">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="O30">
-        <v>0.3571428571428572</v>
+        <v>1</v>
       </c>
       <c r="P30" t="b">
         <v>1</v>
@@ -2278,37 +2278,37 @@
         <v>66</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="G31">
+        <v>2</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0.7071067811865476</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
         <v>3</v>
       </c>
-      <c r="H31">
-        <v>-0.6000000000000001</v>
-      </c>
-      <c r="I31">
-        <v>0.5477225575051661</v>
-      </c>
-      <c r="J31">
-        <v>3</v>
-      </c>
-      <c r="K31">
-        <v>4</v>
-      </c>
       <c r="L31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M31">
         <v>1</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="O31">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="P31" t="b">
         <v>1</v>
@@ -2387,37 +2387,37 @@
         <v>66</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I33">
-        <v>0.447213595499958</v>
+        <v>0.7071067811865476</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="K33">
+        <v>3</v>
+      </c>
+      <c r="L33">
         <v>2</v>
       </c>
-      <c r="L33">
-        <v>1</v>
-      </c>
       <c r="M33">
         <v>1</v>
       </c>
       <c r="N33">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="O33">
-        <v>5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="P33" t="b">
         <v>1</v>
@@ -2443,25 +2443,25 @@
         <v>66</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>-0.7999999999999998</v>
+        <v>0.4</v>
       </c>
       <c r="I34">
-        <v>0.4472135954999579</v>
+        <v>0.5477225575051662</v>
       </c>
       <c r="J34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L34">
         <v>1</v>
@@ -2470,10 +2470,10 @@
         <v>1</v>
       </c>
       <c r="N34">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="O34">
-        <v>1.666666666666667</v>
+        <v>2.5</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
@@ -2499,37 +2499,37 @@
         <v>66</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F35">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H35">
-        <v>0.2</v>
+        <v>0.4000000000000004</v>
       </c>
       <c r="I35">
-        <v>0.447213595499958</v>
+        <v>0.8944271909999159</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K35">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M35">
         <v>1</v>
       </c>
       <c r="N35">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="O35">
-        <v>2.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="P35" t="b">
         <v>1</v>
@@ -2555,37 +2555,37 @@
         <v>66</v>
       </c>
       <c r="E36">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>15</v>
+        <v>0.8</v>
       </c>
       <c r="G36">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="I36">
-        <v>0.7071067811865476</v>
+        <v>0.447213595499958</v>
       </c>
       <c r="J36">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K36">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="L36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M36">
         <v>1</v>
       </c>
       <c r="N36">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="O36">
-        <v>0.8333333333333334</v>
+        <v>2.5</v>
       </c>
       <c r="P36" t="b">
         <v>1</v>
@@ -2611,16 +2611,16 @@
         <v>66</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>0.6</v>
+        <v>-0.6</v>
       </c>
       <c r="I37">
         <v>0.5477225575051662</v>
@@ -2679,7 +2679,7 @@
         <v>-0.2</v>
       </c>
       <c r="I38">
-        <v>0.4472135954999579</v>
+        <v>0.447213595499958</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -2694,10 +2694,10 @@
         <v>1</v>
       </c>
       <c r="N38">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="O38">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="P38" t="b">
         <v>1</v>
@@ -2714,46 +2714,46 @@
         <v>55</v>
       </c>
       <c r="B39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C39" t="s">
         <v>64</v>
       </c>
       <c r="D39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>52.06818961625282</v>
       </c>
       <c r="F39">
-        <v>0.8</v>
+        <v>52.06818961625282</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>52.11914221218962</v>
       </c>
       <c r="H39">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>0.447213595499958</v>
+        <v>0.09260659331828282</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>51.91801354401807</v>
       </c>
       <c r="K39">
-        <v>1</v>
+        <v>52.13255079006773</v>
       </c>
       <c r="L39">
-        <v>1</v>
+        <v>0.2145372460496588</v>
       </c>
       <c r="M39">
-        <v>1</v>
+        <v>0.1501760722347498</v>
       </c>
       <c r="N39">
-        <v>0.8</v>
+        <v>1.323492690170848</v>
       </c>
       <c r="O39">
-        <v>1.25</v>
+        <v>0.1134695139233174</v>
       </c>
       <c r="P39" t="b">
         <v>1</v>
@@ -2779,37 +2779,37 @@
         <v>67</v>
       </c>
       <c r="E40">
-        <v>50.93213701657459</v>
+        <v>45.01181038374718</v>
       </c>
       <c r="F40">
-        <v>50.93213701657459</v>
+        <v>45.01181038374718</v>
       </c>
       <c r="G40">
-        <v>50.98197790055249</v>
+        <v>45.05585778781037</v>
       </c>
       <c r="H40">
-        <v>7.105427357601002E-15</v>
+        <v>0</v>
       </c>
       <c r="I40">
-        <v>0.09058605137392141</v>
+        <v>0.08005637318003306</v>
       </c>
       <c r="J40">
-        <v>50.78523756906078</v>
+        <v>44.88198645598194</v>
       </c>
       <c r="K40">
-        <v>50.99509392265193</v>
+        <v>45.06744920993228</v>
       </c>
       <c r="L40">
-        <v>0.2098563535911495</v>
+        <v>0.1854627539503397</v>
       </c>
       <c r="M40">
-        <v>0.1468994475138032</v>
+        <v>0.1298239277652371</v>
       </c>
       <c r="N40">
-        <v>1.323492690170848</v>
+        <v>1.064148394560983</v>
       </c>
       <c r="O40">
-        <v>0.1109937732220041</v>
+        <v>0.121997954823581</v>
       </c>
       <c r="P40" t="b">
         <v>1</v>
@@ -2826,46 +2826,46 @@
         <v>57</v>
       </c>
       <c r="B41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C41" t="s">
         <v>64</v>
       </c>
       <c r="D41" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E41">
-        <v>46.14786298342541</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>46.14786298342542</v>
+        <v>1</v>
       </c>
       <c r="G41">
-        <v>46.19302209944752</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>7.105427357601002E-15</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>0.08207691512439286</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>46.01476243093924</v>
+        <v>1</v>
       </c>
       <c r="K41">
-        <v>46.20490607734807</v>
+        <v>1</v>
       </c>
       <c r="L41">
-        <v>0.1901436464088349</v>
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>0.1331005524861766</v>
+        <v>0</v>
       </c>
       <c r="N41">
-        <v>1.064148394560983</v>
+        <v>0.8</v>
       </c>
       <c r="O41">
-        <v>0.1250770598973534</v>
+        <v>0</v>
       </c>
       <c r="P41" t="b">
         <v>1</v>
@@ -2891,13 +2891,13 @@
         <v>66</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -2906,10 +2906,10 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2918,7 +2918,7 @@
         <v>0</v>
       </c>
       <c r="N42">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -2947,13 +2947,13 @@
         <v>66</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -2962,10 +2962,10 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43">
         <v>0</v>
